--- a/astro-site/public/dl/restaurant-checklist-templates/08-restaurant-opening-closing-checklist.xlsx
+++ b/astro-site/public/dl/restaurant-checklist-templates/08-restaurant-opening-closing-checklist.xlsx
@@ -651,7 +651,7 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>▸ This is the checklist for the WHOLE RESTAURANT: what gets opened and closed for the entire building, not for each area. Use it as the frame of the day.</t>
+          <t>▸ This is the checklist for the WHOLE RESTAURANT: what gets opened and closed for the entire building, not for each area. Use it as the backbone of the day.</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
     <row r="36" ht="31" customHeight="1">
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the FRAME of the day.</t>
+          <t>▸ 08-restaurant-opening-closing-checklist.xlsx — checklist for the WHOLE RESTAURANT: it is the BACKBONE of the day.</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
     <row r="40" ht="48" customHeight="1">
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>▸ You are in 08-restaurant-opening-closing-checklist.xlsx: this IS the frame of the day — the MILESTONE of opening and closing the building; the DETAIL of each zone is in 01-opening-closing-checklists-kitchen-foh-bar.xlsx and the MONEY in 09-cash-drawer-opening-closing.xlsx.</t>
+          <t>▸ You are in 08-restaurant-opening-closing-checklist.xlsx: this IS the backbone of the day — the MILESTONE of opening and closing the building; the DETAIL of each zone is in 01-opening-closing-checklists-kitchen-foh-bar.xlsx and the MONEY in 09-cash-drawer-opening-closing.xlsx.</t>
         </is>
       </c>
     </row>
